--- a/output/Hunan/娄底市_news.xlsx
+++ b/output/Hunan/娄底市_news.xlsx
@@ -588,7 +588,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,13 +599,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1073,152 +1066,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1227,6 +1220,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1669,9 +1663,7 @@
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
+      <c r="N2"/>
       <c r="O2" t="s">
         <v>24</v>
       </c>
@@ -1719,9 +1711,7 @@
       <c r="M3">
         <v>1</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
+      <c r="N3"/>
       <c r="O3" t="s">
         <v>32</v>
       </c>
@@ -1769,9 +1759,7 @@
       <c r="M4">
         <v>2</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
+      <c r="N4"/>
       <c r="O4" t="s">
         <v>37</v>
       </c>
@@ -1819,9 +1807,7 @@
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
+      <c r="N5"/>
       <c r="O5" t="s">
         <v>45</v>
       </c>
@@ -1869,9 +1855,7 @@
       <c r="M6">
         <v>0</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
+      <c r="N6"/>
       <c r="O6" t="s">
         <v>50</v>
       </c>
@@ -1919,9 +1903,7 @@
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
+      <c r="N7"/>
       <c r="O7" t="s">
         <v>54</v>
       </c>
@@ -1969,9 +1951,7 @@
       <c r="M8">
         <v>1</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
+      <c r="N8"/>
       <c r="O8" t="s">
         <v>59</v>
       </c>
@@ -2019,9 +1999,7 @@
       <c r="M9">
         <v>15</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
+      <c r="N9"/>
       <c r="O9" t="s">
         <v>66</v>
       </c>
@@ -2069,9 +2047,7 @@
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
+      <c r="N10"/>
       <c r="O10" t="s">
         <v>72</v>
       </c>
@@ -2119,9 +2095,7 @@
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
+      <c r="N11"/>
       <c r="O11" t="s">
         <v>76</v>
       </c>
@@ -2169,9 +2143,7 @@
       <c r="M12">
         <v>1</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
+      <c r="N12"/>
       <c r="O12" t="s">
         <v>78</v>
       </c>
@@ -2219,9 +2191,7 @@
       <c r="M13">
         <v>0</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
+      <c r="N13"/>
       <c r="O13" t="s">
         <v>80</v>
       </c>
@@ -2269,9 +2239,7 @@
       <c r="M14">
         <v>1</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
+      <c r="N14"/>
       <c r="O14" t="s">
         <v>82</v>
       </c>
@@ -2319,9 +2287,7 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
+      <c r="N15"/>
       <c r="O15" t="s">
         <v>84</v>
       </c>
@@ -2369,9 +2335,7 @@
       <c r="M16">
         <v>2</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
+      <c r="N16"/>
       <c r="O16" t="s">
         <v>86</v>
       </c>
@@ -2419,9 +2383,7 @@
       <c r="M17">
         <v>0</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
+      <c r="N17"/>
       <c r="O17" t="s">
         <v>92</v>
       </c>
@@ -2469,9 +2431,7 @@
       <c r="M18">
         <v>3</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
+      <c r="N18"/>
       <c r="O18" t="s">
         <v>95</v>
       </c>
@@ -2519,9 +2479,7 @@
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
+      <c r="N19"/>
       <c r="O19" t="s">
         <v>100</v>
       </c>
@@ -2569,9 +2527,7 @@
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
+      <c r="N20"/>
       <c r="O20" t="s">
         <v>104</v>
       </c>
@@ -2619,9 +2575,7 @@
       <c r="M21">
         <v>0</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
+      <c r="N21"/>
       <c r="O21" t="s">
         <v>106</v>
       </c>
@@ -2669,9 +2623,7 @@
       <c r="M22">
         <v>0</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
+      <c r="N22"/>
       <c r="O22" t="s">
         <v>111</v>
       </c>
@@ -2719,9 +2671,7 @@
       <c r="M23">
         <v>0</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
+      <c r="N23"/>
       <c r="O23" t="s">
         <v>113</v>
       </c>
@@ -2769,9 +2719,7 @@
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
+      <c r="N24"/>
       <c r="O24" t="s">
         <v>117</v>
       </c>
@@ -2819,9 +2767,7 @@
       <c r="M25">
         <v>0</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
+      <c r="N25"/>
       <c r="O25" t="s">
         <v>120</v>
       </c>
@@ -2869,9 +2815,7 @@
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
+      <c r="N26"/>
       <c r="O26" t="s">
         <v>122</v>
       </c>
@@ -2919,9 +2863,7 @@
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
+      <c r="N27"/>
       <c r="O27" t="s">
         <v>124</v>
       </c>
@@ -2969,9 +2911,7 @@
       <c r="M28">
         <v>0</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
+      <c r="N28"/>
       <c r="O28" t="s">
         <v>126</v>
       </c>
@@ -3019,9 +2959,7 @@
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
+      <c r="N29"/>
       <c r="O29" t="s">
         <v>128</v>
       </c>
@@ -3069,9 +3007,7 @@
       <c r="M30">
         <v>0</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
+      <c r="N30"/>
       <c r="O30" t="s">
         <v>130</v>
       </c>
@@ -3119,9 +3055,7 @@
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
+      <c r="N31"/>
       <c r="O31" t="s">
         <v>132</v>
       </c>
@@ -3169,9 +3103,7 @@
       <c r="M32">
         <v>0</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
+      <c r="N32"/>
       <c r="O32" t="s">
         <v>133</v>
       </c>
@@ -3219,9 +3151,7 @@
       <c r="M33">
         <v>0</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
+      <c r="N33"/>
       <c r="O33" t="s">
         <v>135</v>
       </c>
@@ -3269,9 +3199,7 @@
       <c r="M34">
         <v>0</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
+      <c r="N34"/>
       <c r="O34" t="s">
         <v>137</v>
       </c>
@@ -3319,9 +3247,7 @@
       <c r="M35">
         <v>0</v>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
+      <c r="N35"/>
       <c r="O35" t="s">
         <v>139</v>
       </c>
@@ -3369,9 +3295,7 @@
       <c r="M36">
         <v>0</v>
       </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
+      <c r="N36"/>
       <c r="O36" t="s">
         <v>141</v>
       </c>
@@ -3419,9 +3343,7 @@
       <c r="M37">
         <v>0</v>
       </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
+      <c r="N37"/>
       <c r="O37" t="s">
         <v>144</v>
       </c>
@@ -3469,9 +3391,7 @@
       <c r="M38">
         <v>0</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
+      <c r="N38"/>
       <c r="O38" t="s">
         <v>146</v>
       </c>
@@ -3519,9 +3439,7 @@
       <c r="M39">
         <v>0</v>
       </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
+      <c r="N39"/>
       <c r="O39" t="s">
         <v>148</v>
       </c>
@@ -3569,9 +3487,7 @@
       <c r="M40">
         <v>0</v>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
+      <c r="N40"/>
       <c r="O40" t="s">
         <v>150</v>
       </c>
@@ -3619,9 +3535,7 @@
       <c r="M41">
         <v>0</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
+      <c r="N41"/>
       <c r="O41" t="s">
         <v>152</v>
       </c>
@@ -3669,9 +3583,7 @@
       <c r="M42">
         <v>0</v>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
+      <c r="N42"/>
       <c r="O42" t="s">
         <v>154</v>
       </c>
@@ -3719,9 +3631,7 @@
       <c r="M43">
         <v>0</v>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
+      <c r="N43"/>
       <c r="O43" t="s">
         <v>156</v>
       </c>
@@ -3769,9 +3679,7 @@
       <c r="M44">
         <v>0</v>
       </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
+      <c r="N44"/>
       <c r="O44" t="s">
         <v>158</v>
       </c>
@@ -3819,9 +3727,7 @@
       <c r="M45">
         <v>0</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
+      <c r="N45"/>
       <c r="O45" t="s">
         <v>160</v>
       </c>
@@ -3869,9 +3775,7 @@
       <c r="M46">
         <v>0</v>
       </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
+      <c r="N46"/>
       <c r="O46" t="s">
         <v>165</v>
       </c>
@@ -3919,10 +3823,8 @@
       <c r="M47">
         <v>0</v>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47" t="s">
+      <c r="N47"/>
+      <c r="O47" s="4" t="s">
         <v>169</v>
       </c>
       <c r="P47" t="s">
@@ -3969,9 +3871,7 @@
       <c r="M48">
         <v>3</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
+      <c r="N48"/>
       <c r="O48" t="s">
         <v>173</v>
       </c>
@@ -4019,9 +3919,7 @@
       <c r="M49">
         <v>0</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
+      <c r="N49"/>
       <c r="O49" t="s">
         <v>178</v>
       </c>
@@ -4069,9 +3967,7 @@
       <c r="M50">
         <v>0</v>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
+      <c r="N50"/>
       <c r="O50" t="s">
         <v>180</v>
       </c>
@@ -4104,9 +4000,7 @@
       <c r="H51" t="s">
         <v>44</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
+      <c r="I51"/>
       <c r="J51" s="1" t="s">
         <v>181</v>
       </c>
@@ -4116,9 +4010,7 @@
       <c r="L51">
         <v>806</v>
       </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
+      <c r="M51"/>
       <c r="N51">
         <v>2</v>
       </c>
@@ -4129,6 +4021,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="O51" r:id="rId1" display="http://data.hnloudi.gov.cn:51182/oportal/api/8030445304b14ffeaff948063a0eb04e/detail"/>
+    <hyperlink ref="O47" r:id="rId2" display="http://data.hnloudi.gov.cn:51182/oportal/catalog/5150b5289a9b4e1f97b0493ef6ab1cae"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
